--- a/Result/profitability/1108.xlsx
+++ b/Result/profitability/1108.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3962499999999999</v>
+        <v>0.36875</v>
       </c>
       <c r="N2" t="n">
-        <v>17.27125</v>
+        <v>16.42625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.35875</v>
+        <v>0.325</v>
       </c>
       <c r="N3" t="n">
-        <v>16.41</v>
+        <v>15.17375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3124999999999999</v>
+        <v>0.27875</v>
       </c>
       <c r="N4" t="n">
-        <v>15.1025</v>
+        <v>13.89625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.24125</v>
+        <v>0.07374999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>13.90875</v>
+        <v>12.3575</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07124999999999997</v>
+        <v>0.03999999999999997</v>
       </c>
       <c r="N6" t="n">
-        <v>12.89625</v>
+        <v>11.58375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03874999999999997</v>
+        <v>0.02499999999999997</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5125</v>
+        <v>12.02875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.08</v>
       </c>
       <c r="M8" t="n">
-        <v>0.02874999999999997</v>
+        <v>0.01374999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>12.58875</v>
+        <v>11.8075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>923</v>
+      </c>
+      <c r="D75" t="n">
+        <v>832</v>
+      </c>
+      <c r="E75" t="n">
+        <v>91</v>
+      </c>
+      <c r="F75" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>44</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>44</v>
+      </c>
+      <c r="K75" t="n">
+        <v>19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3724999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.30625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7058823529411764</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3872366790582403</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9640287769784173</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5565022421524664</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
